--- a/results/trace_final20_temp06_3b7b_all_methods_results.xlsx
+++ b/results/trace_final20_temp06_3b7b_all_methods_results.xlsx
@@ -733,13 +733,13 @@
         <v>1272</v>
       </c>
       <c r="C16" t="n">
-        <v>60.51</v>
+        <v>68.19</v>
       </c>
       <c r="D16" t="n">
-        <v>58.75</v>
+        <v>64.02</v>
       </c>
       <c r="E16" t="n">
-        <v>63.44</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="17">
@@ -845,13 +845,13 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>37.72</v>
+        <v>38.102</v>
       </c>
       <c r="D22" t="n">
-        <v>41.42</v>
+        <v>41.6845</v>
       </c>
       <c r="E22" t="n">
-        <v>40.1</v>
+        <v>40.80499999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1312,22 +1312,22 @@
         <v>1272</v>
       </c>
       <c r="C16" t="n">
-        <v>72.8</v>
+        <v>72.64</v>
       </c>
       <c r="D16" t="n">
-        <v>77.73</v>
+        <v>77.86</v>
       </c>
       <c r="E16" t="n">
-        <v>75.23999999999999</v>
+        <v>75.31</v>
       </c>
       <c r="F16" t="n">
         <v>81.05</v>
       </c>
       <c r="G16" t="n">
-        <v>8.41</v>
+        <v>8.25</v>
       </c>
       <c r="H16" t="n">
-        <v>36.87</v>
+        <v>67.84999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1383,7 +1383,7 @@
         <v>69.68000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>11.44</v>
+        <v>78.64</v>
       </c>
     </row>
     <row r="19">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>46.34</v>
+        <v>46.331</v>
       </c>
       <c r="D22" t="n">
-        <v>50.93</v>
+        <v>50.938</v>
       </c>
       <c r="E22" t="n">
-        <v>47.19</v>
+        <v>47.1975</v>
       </c>
       <c r="F22" t="n">
-        <v>47.26</v>
+        <v>47.262</v>
       </c>
       <c r="G22" t="n">
-        <v>43.52</v>
+        <v>43.512</v>
       </c>
       <c r="H22" t="n">
-        <v>45.4</v>
+        <v>50.3105</v>
       </c>
     </row>
   </sheetData>
@@ -1507,7 +1507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1570,6 +1570,18 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>screenspot_table_repair</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Re-parsed cached predictions for ScreenSpot positional clicks and TableVQABench final-answer wrappers; no generation/judge rerun.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/trace_final20_temp06_3b7b_all_methods_results.xlsx
+++ b/results/trace_final20_temp06_3b7b_all_methods_results.xlsx
@@ -809,13 +809,13 @@
         <v>1168</v>
       </c>
       <c r="C20" t="n">
-        <v>17.32</v>
+        <v>18.49</v>
       </c>
       <c r="D20" t="n">
-        <v>18.86</v>
+        <v>21.03</v>
       </c>
       <c r="E20" t="n">
-        <v>17.38</v>
+        <v>19.18</v>
       </c>
     </row>
     <row r="21">
@@ -845,13 +845,13 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>38.102</v>
+        <v>38.1605</v>
       </c>
       <c r="D22" t="n">
-        <v>41.6845</v>
+        <v>41.79299999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>40.80499999999999</v>
+        <v>40.895</v>
       </c>
     </row>
   </sheetData>
@@ -1424,22 +1424,22 @@
         <v>1168</v>
       </c>
       <c r="C20" t="n">
-        <v>19.35</v>
+        <v>21.66</v>
       </c>
       <c r="D20" t="n">
-        <v>22.32</v>
+        <v>24.49</v>
       </c>
       <c r="E20" t="n">
-        <v>19.18</v>
+        <v>21.4</v>
       </c>
       <c r="F20" t="n">
-        <v>18.49</v>
+        <v>22.09</v>
       </c>
       <c r="G20" t="n">
-        <v>20.21</v>
+        <v>23.46</v>
       </c>
       <c r="H20" t="n">
-        <v>23.54</v>
+        <v>27.91</v>
       </c>
     </row>
     <row r="21">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>46.331</v>
+        <v>46.4465</v>
       </c>
       <c r="D22" t="n">
-        <v>50.938</v>
+        <v>51.04649999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>47.1975</v>
+        <v>47.3085</v>
       </c>
       <c r="F22" t="n">
-        <v>47.262</v>
+        <v>47.442</v>
       </c>
       <c r="G22" t="n">
-        <v>43.512</v>
+        <v>43.6745</v>
       </c>
       <c r="H22" t="n">
-        <v>50.3105</v>
+        <v>50.529</v>
       </c>
     </row>
   </sheetData>
@@ -1507,7 +1507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1582,6 +1582,18 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>visualpuzzles_repair</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Re-scored cached Qwen3 extraction outputs with VisualPuzzles A-D option contract; no generation/judge rerun.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
